--- a/ibkr-gerchik-bot/memory/reports/premarket_levels_20260504.xlsx
+++ b/ibkr-gerchik-bot/memory/reports/premarket_levels_20260504.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -723,33 +723,33 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BBBY</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>04/28/26</t>
+          <t>04/22/26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>04/28/26</t>
+          <t>04/22/26</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7.7</v>
+        <v>10.86</v>
       </c>
       <c r="E8" t="n">
-        <v>7.64</v>
+        <v>10.77</v>
       </c>
       <c r="F8" t="n">
-        <v>7.76</v>
+        <v>10.94</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>7.86</v>
+        <v>8.73</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -758,250 +758,250 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>abnormal_candle, consolidation, historical, structural</t>
+          <t>abnormal_candle, consolidation, gap, historical, structural</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BBBY</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>04/20/26</t>
+          <t>04/27/26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>04/20/26</t>
+          <t>04/23/26</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.27</v>
+        <v>7.1</v>
       </c>
       <c r="E9" t="n">
-        <v>6.21</v>
+        <v>7.02</v>
       </c>
       <c r="F9" t="n">
-        <v>6.33</v>
+        <v>7.28</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>6.86</v>
+        <v>16.83</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>abnormal_candle</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>historical, structural</t>
+          <t>abnormal_candle, gap, structural</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SANM</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>04/28/26</t>
+          <t>04/27/26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>04/28/26</t>
+          <t>04/23/26</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>230.56</v>
+        <v>6.64</v>
       </c>
       <c r="E10" t="n">
-        <v>226.99</v>
+        <v>6.56</v>
       </c>
       <c r="F10" t="n">
-        <v>232.57</v>
+        <v>6.88</v>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>12.97</v>
+        <v>14.86</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>abnormal_candle</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>abnormal_candle, consolidation, historical, structural</t>
+          <t>gap</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SANM</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>04/29/26</t>
+          <t>04/07/26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>04/28/26</t>
+          <t>04/07/26</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>217.67</v>
+        <v>6.46</v>
       </c>
       <c r="E11" t="n">
-        <v>211.78</v>
+        <v>6.38</v>
       </c>
       <c r="F11" t="n">
-        <v>219.68</v>
+        <v>6.54</v>
       </c>
       <c r="G11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>28</v>
+        <v>12.86</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>abnormal_candle</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>abnormal_candle, historical, structural</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SANM</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>04/30/26</t>
+          <t>05/01/26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>04/28/26</t>
+          <t>04/07/26</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>208.67</v>
+        <v>6.16</v>
       </c>
       <c r="E12" t="n">
-        <v>202.97</v>
+        <v>6.08</v>
       </c>
       <c r="F12" t="n">
-        <v>210.68</v>
+        <v>6.24</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>13</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>historical, structural</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SANM</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>04/16/26</t>
+          <t>04/29/26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>04/16/26</t>
+          <t>04/07/26</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>172.35</v>
+        <v>5.93</v>
       </c>
       <c r="E13" t="n">
-        <v>166.96</v>
+        <v>5.78</v>
       </c>
       <c r="F13" t="n">
-        <v>174.36</v>
+        <v>6.01</v>
       </c>
       <c r="G13" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>33.76</v>
+        <v>23.97</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>abnormal_candle</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>abnormal_candle, gap, historical, structural</t>
+          <t>gap</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEI</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>04/28/26</t>
+          <t>04/10/26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>04/28/26</t>
+          <t>04/07/26</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>81.23999999999999</v>
+        <v>5.23</v>
       </c>
       <c r="E14" t="n">
-        <v>79.97</v>
+        <v>5.15</v>
       </c>
       <c r="F14" t="n">
-        <v>82.04000000000001</v>
+        <v>5.36</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H14" t="n">
-        <v>12.9</v>
+        <v>23</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1010,40 +1010,40 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>abnormal_candle, consolidation, historical, structural</t>
+          <t>abnormal_candle, historical, structural</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEI</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>04/28/26</t>
+          <t>04/22/26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>04/28/26</t>
+          <t>04/07/26</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>77.12</v>
+        <v>4.88</v>
       </c>
       <c r="E15" t="n">
-        <v>76.31999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="F15" t="n">
-        <v>77.92</v>
+        <v>4.96</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>6.93</v>
+        <v>12.69</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1059,42 +1059,4620 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>AGPU</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>04/01/26</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>04/01/26</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>abnormal_candle, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AGPU</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>02/25/26</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>02/10/26</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>gap, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AGPU</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>03/19/26</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>03/19/26</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ALOY</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>03/05/26</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>26.64</v>
+      </c>
+      <c r="E19" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="F19" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>abnormal_candle, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ALOY</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>03/05/26</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="E20" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="F20" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ALOY</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>03/05/26</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="E21" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="F21" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ALOY</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="E22" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="F22" t="n">
+        <v>24.52</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ALOY</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>03/06/26</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="E23" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="F23" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ALOY</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="E24" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="F24" t="n">
+        <v>21.23</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ALOY</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>03/05/26</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="E25" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="F25" t="n">
+        <v>20.85</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>abnormal_candle, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ALOY</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>02/27/26</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>02/27/26</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="E26" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="F26" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>abnormal_candle, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ALOY</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>02/24/26</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>02/24/26</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="E27" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="F27" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>abnormal_candle, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ALOY</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>03/02/26</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>02/24/26</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="E28" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="F28" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ALOY</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>03/12/26</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>02/24/26</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="E29" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="F29" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ALOY</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>03/12/26</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>02/24/26</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="E30" t="n">
+        <v>16.46</v>
+      </c>
+      <c r="F30" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ALOY</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>02/26/26</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>02/24/26</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="E31" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="F31" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="G31" t="n">
+        <v>30</v>
+      </c>
+      <c r="H31" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>abnormal_candle, gap, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ALOY</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>02/26/26</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>02/23/26</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="E32" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="F32" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="G32" t="n">
+        <v>18</v>
+      </c>
+      <c r="H32" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ALOY</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>03/09/26</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>02/23/26</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="E33" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="F33" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ALOY</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>03/25/26</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>02/09/26</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="E34" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="F34" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="G34" t="n">
+        <v>17</v>
+      </c>
+      <c r="H34" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ALOY</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>03/30/26</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>02/12/26</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="E35" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="F35" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="G35" t="n">
+        <v>44</v>
+      </c>
+      <c r="H35" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>04/24/26</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>04/24/26</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>263.34</v>
+      </c>
+      <c r="F36" t="n">
+        <v>265.66</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>04/30/26</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>04/17/26</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>256.16</v>
+      </c>
+      <c r="E37" t="n">
+        <v>255</v>
+      </c>
+      <c r="F37" t="n">
+        <v>257.79</v>
+      </c>
+      <c r="G37" t="n">
+        <v>25</v>
+      </c>
+      <c r="H37" t="n">
+        <v>41.93</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>abnormal_candle, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>04/22/26</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>04/14/26</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>249.91</v>
+      </c>
+      <c r="E38" t="n">
+        <v>247.12</v>
+      </c>
+      <c r="F38" t="n">
+        <v>251.07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>19</v>
+      </c>
+      <c r="H38" t="n">
+        <v>44.73</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>04/20/26</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>04/14/26</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>245.36</v>
+      </c>
+      <c r="E39" t="n">
+        <v>243.04</v>
+      </c>
+      <c r="F39" t="n">
+        <v>246.52</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>04/10/26</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>04/10/26</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>240.43</v>
+      </c>
+      <c r="E40" t="n">
+        <v>239.27</v>
+      </c>
+      <c r="F40" t="n">
+        <v>241.59</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>04/09/26</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>04/08/26</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>225.23</v>
+      </c>
+      <c r="E41" t="n">
+        <v>222.53</v>
+      </c>
+      <c r="F41" t="n">
+        <v>226.39</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4</v>
+      </c>
+      <c r="H41" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>04/09/26</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>03/05/26</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>221.25</v>
+      </c>
+      <c r="E42" t="n">
+        <v>217.78</v>
+      </c>
+      <c r="F42" t="n">
+        <v>222.41</v>
+      </c>
+      <c r="G42" t="n">
+        <v>4</v>
+      </c>
+      <c r="H42" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BBBY</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>04/28/26</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>04/28/26</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E43" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>abnormal_candle, consolidation, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BBBY</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>04/20/26</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>04/20/26</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="F44" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BIRD</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>24.31</v>
+      </c>
+      <c r="E45" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="F45" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>abnormal_candle, consolidation, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BIRD</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>04/16/26</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="E46" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="F46" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4</v>
+      </c>
+      <c r="H46" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>abnormal_candle, gap, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BIRD</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>04/17/26</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="E47" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="F47" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>abnormal_candle, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BIRD</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>04/20/26</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E48" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="F48" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="G48" t="n">
+        <v>8</v>
+      </c>
+      <c r="H48" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>abnormal_candle, gap, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BIRD</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>04/21/26</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="E49" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="F49" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>abnormal_candle, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BIRD</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>04/20/26</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="E50" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="F50" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BIRD</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>04/17/26</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="E51" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="F51" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="G51" t="n">
+        <v>6</v>
+      </c>
+      <c r="H51" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>abnormal_candle, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BIRD</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>04/22/26</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="E52" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="F52" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3</v>
+      </c>
+      <c r="H52" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>abnormal_candle, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BIRD</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>04/21/26</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E53" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="F53" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="G53" t="n">
+        <v>9</v>
+      </c>
+      <c r="H53" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>abnormal_candle, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BIRD</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>04/23/26</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="E54" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="F54" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4</v>
+      </c>
+      <c r="H54" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BIRD</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>04/24/26</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="E55" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="F55" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="G55" t="n">
+        <v>4</v>
+      </c>
+      <c r="H55" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BIRD</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>04/22/26</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="E56" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="F56" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="G56" t="n">
+        <v>12</v>
+      </c>
+      <c r="H56" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>abnormal_candle, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BIRD</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>05/01/26</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="E57" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="F57" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="G57" t="n">
+        <v>10</v>
+      </c>
+      <c r="H57" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BIRD</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="E58" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="F58" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="G58" t="n">
+        <v>6</v>
+      </c>
+      <c r="H58" t="n">
+        <v>11</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>abnormal_candle, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BIRD</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>03/11/26</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>03/10/26</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E59" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>EUR.USD</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>03/19/26</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G60" t="n">
+        <v>70</v>
+      </c>
+      <c r="H60" t="n">
+        <v>75.36</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>abnormal_candle, consolidation, historical, limit_player, mirror, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>EUR.USD</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>03/13/26</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G61" t="n">
+        <v>32</v>
+      </c>
+      <c r="H61" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>abnormal_candle, historical, limit_player, mirror, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ISPC</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>02/13/26</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>02/13/26</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E62" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="F62" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="G62" t="n">
+        <v>4</v>
+      </c>
+      <c r="H62" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>abnormal_candle, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ISPC</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>02/24/26</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>02/23/26</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="E63" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="G63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H63" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ISPC</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>03/18/26</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>03/16/26</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="E64" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="F64" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="G64" t="n">
+        <v>5</v>
+      </c>
+      <c r="H64" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ISPC</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>03/16/26</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>03/16/26</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="E65" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="F65" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="G65" t="n">
+        <v>38</v>
+      </c>
+      <c r="H65" t="n">
+        <v>52.76</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>abnormal_candle, gap, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MRLN</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>04/17/26</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>04/16/26</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="E66" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="F66" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="G66" t="n">
+        <v>7</v>
+      </c>
+      <c r="H66" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>abnormal_candle, consolidation, gap, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MRLN</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>04/17/26</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>04/16/26</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="E67" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F67" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MRLN</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>03/25/26</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="E68" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="F68" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="G68" t="n">
+        <v>6</v>
+      </c>
+      <c r="H68" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>abnormal_candle, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MRLN</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>04/21/26</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>03/25/26</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="E69" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="F69" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="G69" t="n">
+        <v>29</v>
+      </c>
+      <c r="H69" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>abnormal_candle, gap, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MRLN</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>03/17/26</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>03/17/26</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="E70" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="F70" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="G70" t="n">
+        <v>12</v>
+      </c>
+      <c r="H70" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>abnormal_candle, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>02/10/26</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>02/10/26</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>423.68</v>
+      </c>
+      <c r="E71" t="n">
+        <v>422.54</v>
+      </c>
+      <c r="F71" t="n">
+        <v>425.96</v>
+      </c>
+      <c r="G71" t="n">
+        <v>38</v>
+      </c>
+      <c r="H71" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>gap, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>04/17/26</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>02/10/26</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>420.26</v>
+      </c>
+      <c r="E72" t="n">
+        <v>418.47</v>
+      </c>
+      <c r="F72" t="n">
+        <v>421.4</v>
+      </c>
+      <c r="G72" t="n">
+        <v>40</v>
+      </c>
+      <c r="H72" t="n">
+        <v>52</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>05/01/26</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>02/09/26</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>407.78</v>
+      </c>
+      <c r="E73" t="n">
+        <v>406.35</v>
+      </c>
+      <c r="F73" t="n">
+        <v>408.92</v>
+      </c>
+      <c r="G73" t="n">
+        <v>24</v>
+      </c>
+      <c r="H73" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>gap, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>02/26/26</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>02/09/26</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>404.71</v>
+      </c>
+      <c r="E74" t="n">
+        <v>403.26</v>
+      </c>
+      <c r="F74" t="n">
+        <v>405.85</v>
+      </c>
+      <c r="G74" t="n">
+        <v>51</v>
+      </c>
+      <c r="H74" t="n">
+        <v>80.93000000000001</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>gap, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>02/06/26</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>393.28</v>
+      </c>
+      <c r="E75" t="n">
+        <v>389.74</v>
+      </c>
+      <c r="F75" t="n">
+        <v>394.42</v>
+      </c>
+      <c r="G75" t="n">
+        <v>27</v>
+      </c>
+      <c r="H75" t="n">
+        <v>40.53</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>04/08/26</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>02/23/26</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>385</v>
+      </c>
+      <c r="E76" t="n">
+        <v>383.84</v>
+      </c>
+      <c r="F76" t="n">
+        <v>388.35</v>
+      </c>
+      <c r="G76" t="n">
+        <v>18</v>
+      </c>
+      <c r="H76" t="n">
+        <v>29.53</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>gap, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>02/24/26</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>02/24/26</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>381.71</v>
+      </c>
+      <c r="E77" t="n">
+        <v>378.98</v>
+      </c>
+      <c r="F77" t="n">
+        <v>382.85</v>
+      </c>
+      <c r="G77" t="n">
+        <v>10</v>
+      </c>
+      <c r="H77" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>03/25/26</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>03/24/26</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>376.93</v>
+      </c>
+      <c r="E78" t="n">
+        <v>375.79</v>
+      </c>
+      <c r="F78" t="n">
+        <v>378.07</v>
+      </c>
+      <c r="G78" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>03/25/26</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>03/24/26</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>372.74</v>
+      </c>
+      <c r="E79" t="n">
+        <v>371.15</v>
+      </c>
+      <c r="F79" t="n">
+        <v>373.88</v>
+      </c>
+      <c r="G79" t="n">
+        <v>24</v>
+      </c>
+      <c r="H79" t="n">
+        <v>45.49</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>03/27/26</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>03/27/26</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>361.9</v>
+      </c>
+      <c r="E80" t="n">
+        <v>360.76</v>
+      </c>
+      <c r="F80" t="n">
+        <v>363.04</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2</v>
+      </c>
+      <c r="H80" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>OPTX</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>04/14/26</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>04/13/26</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>12</v>
+      </c>
+      <c r="E81" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="F81" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2</v>
+      </c>
+      <c r="H81" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>OPTX</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>04/13/26</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="E82" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="F82" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="G82" t="n">
+        <v>11</v>
+      </c>
+      <c r="H82" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>gap, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>OPTX</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>04/13/26</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>04/13/26</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="E83" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="F83" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="G83" t="n">
+        <v>9</v>
+      </c>
+      <c r="H83" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>OPTX</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>03/11/26</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>02/06/26</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="E84" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="F84" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="G84" t="n">
+        <v>14</v>
+      </c>
+      <c r="H84" t="n">
+        <v>20</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ROLR</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>04/27/26</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>04/27/26</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="E85" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="F85" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="G85" t="n">
+        <v>3</v>
+      </c>
+      <c r="H85" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>abnormal_candle, consolidation, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ROLR</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>04/14/26</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>04/14/26</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="E86" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="F86" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G86" t="n">
+        <v>4</v>
+      </c>
+      <c r="H86" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>abnormal_candle, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ROLR</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>04/29/26</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>04/14/26</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="E87" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="F87" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="G87" t="n">
+        <v>4</v>
+      </c>
+      <c r="H87" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>abnormal_candle, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ROLR</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>04/29/26</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>04/14/26</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="E88" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="F88" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="G88" t="n">
+        <v>5</v>
+      </c>
+      <c r="H88" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ROLR</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="E89" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F89" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2</v>
+      </c>
+      <c r="H89" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ROLR</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>04/16/26</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E90" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="F90" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="G90" t="n">
+        <v>2</v>
+      </c>
+      <c r="H90" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ROLR</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>04/16/26</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>02/06/26</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>6</v>
+      </c>
+      <c r="E91" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="F91" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="G91" t="n">
+        <v>13</v>
+      </c>
+      <c r="H91" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>abnormal_candle, gap, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SANM</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>04/28/26</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>04/28/26</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>230.56</v>
+      </c>
+      <c r="E92" t="n">
+        <v>226.99</v>
+      </c>
+      <c r="F92" t="n">
+        <v>232.57</v>
+      </c>
+      <c r="G92" t="n">
+        <v>8</v>
+      </c>
+      <c r="H92" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>abnormal_candle, consolidation, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SANM</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>04/29/26</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>04/28/26</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>217.67</v>
+      </c>
+      <c r="E93" t="n">
+        <v>211.78</v>
+      </c>
+      <c r="F93" t="n">
+        <v>219.68</v>
+      </c>
+      <c r="G93" t="n">
+        <v>14</v>
+      </c>
+      <c r="H93" t="n">
+        <v>28</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SANM</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>04/30/26</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>04/28/26</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>208.67</v>
+      </c>
+      <c r="E94" t="n">
+        <v>202.97</v>
+      </c>
+      <c r="F94" t="n">
+        <v>210.68</v>
+      </c>
+      <c r="G94" t="n">
+        <v>7</v>
+      </c>
+      <c r="H94" t="n">
+        <v>13</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>SANM</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>04/16/26</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>04/16/26</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>172.35</v>
+      </c>
+      <c r="E95" t="n">
+        <v>166.96</v>
+      </c>
+      <c r="F95" t="n">
+        <v>174.36</v>
+      </c>
+      <c r="G95" t="n">
+        <v>19</v>
+      </c>
+      <c r="H95" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>abnormal_candle, gap, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
           <t>SEI</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>04/28/26</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>04/28/26</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>81.23999999999999</v>
+      </c>
+      <c r="E96" t="n">
+        <v>79.97</v>
+      </c>
+      <c r="F96" t="n">
+        <v>82.04000000000001</v>
+      </c>
+      <c r="G96" t="n">
+        <v>8</v>
+      </c>
+      <c r="H96" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>abnormal_candle, consolidation, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SEI</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>04/28/26</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>04/28/26</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>77.12</v>
+      </c>
+      <c r="E97" t="n">
+        <v>76.31999999999999</v>
+      </c>
+      <c r="F97" t="n">
+        <v>77.92</v>
+      </c>
+      <c r="G97" t="n">
+        <v>3</v>
+      </c>
+      <c r="H97" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SEI</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
         <is>
           <t>04/29/26</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>04/24/26</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D98" t="n">
         <v>74.44</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E98" t="n">
         <v>73.64</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F98" t="n">
         <v>75.23999999999999</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G98" t="n">
         <v>7</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H98" t="n">
         <v>17</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>gap</t>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SKLZ</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>04/23/26</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>04/23/26</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>20</v>
+      </c>
+      <c r="E99" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="F99" t="n">
+        <v>20.18</v>
+      </c>
+      <c r="G99" t="n">
+        <v>3</v>
+      </c>
+      <c r="H99" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>abnormal_candle, consolidation, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SKLZ</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>04/24/26</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>04/23/26</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E100" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="F100" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="G100" t="n">
+        <v>6</v>
+      </c>
+      <c r="H100" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>abnormal_candle, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SKLZ</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>04/30/26</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>04/23/26</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="E101" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="F101" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="G101" t="n">
+        <v>18</v>
+      </c>
+      <c r="H101" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>abnormal_candle, gap, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SKLZ</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>05/01/26</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>04/23/26</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="E102" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="F102" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="G102" t="n">
+        <v>11</v>
+      </c>
+      <c r="H102" t="n">
+        <v>23</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>SKLZ</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>05/01/26</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>04/23/26</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="E103" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F103" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="G103" t="n">
+        <v>12</v>
+      </c>
+      <c r="H103" t="n">
+        <v>17</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>abnormal_candle, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SKLZ</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>04/27/26</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>04/23/26</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E104" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="F104" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="G104" t="n">
+        <v>25</v>
+      </c>
+      <c r="H104" t="n">
+        <v>49.93</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>abnormal_candle, gap, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>SKLZ</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>04/30/26</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>04/23/26</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="E105" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="F105" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G105" t="n">
+        <v>6</v>
+      </c>
+      <c r="H105" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>abnormal_candle, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SKLZ</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="E106" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="F106" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="G106" t="n">
+        <v>4</v>
+      </c>
+      <c r="H106" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>abnormal_candle, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SKYQ</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>04/13/26</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>04/13/26</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="E107" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="F107" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="G107" t="n">
+        <v>3</v>
+      </c>
+      <c r="H107" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>abnormal_candle, consolidation, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SKYQ</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>04/10/26</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>04/10/26</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="E108" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="F108" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2</v>
+      </c>
+      <c r="H108" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>abnormal_candle, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>SKYQ</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>04/13/26</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>04/10/26</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="E109" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="F109" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="G109" t="n">
+        <v>2</v>
+      </c>
+      <c r="H109" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SKYQ</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>04/14/26</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>04/10/26</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="E110" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F110" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="G110" t="n">
+        <v>2</v>
+      </c>
+      <c r="H110" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SKYQ</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>04/14/26</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>04/10/26</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="E111" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="F111" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="G111" t="n">
+        <v>9</v>
+      </c>
+      <c r="H111" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SKYQ</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>04/17/26</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>04/10/26</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="E112" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F112" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="G112" t="n">
+        <v>7</v>
+      </c>
+      <c r="H112" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SKYQ</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>04/09/26</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>04/09/26</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="E113" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="F113" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="G113" t="n">
+        <v>8</v>
+      </c>
+      <c r="H113" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>abnormal_candle, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SKYQ</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>04/09/26</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="E114" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="F114" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="G114" t="n">
+        <v>8</v>
+      </c>
+      <c r="H114" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>abnormal_candle, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>SKYQ</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>04/07/26</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>04/07/26</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="E115" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F115" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="G115" t="n">
+        <v>20</v>
+      </c>
+      <c r="H115" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>abnormal_candle, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>SKYQ</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>04/20/26</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>04/07/26</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="E116" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="F116" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="G116" t="n">
+        <v>6</v>
+      </c>
+      <c r="H116" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SKYQ</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>04/10/26</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>04/07/26</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="E117" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="F117" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="G117" t="n">
+        <v>5</v>
+      </c>
+      <c r="H117" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>SKYQ</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>04/10/26</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>04/07/26</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="E118" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="F118" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="G118" t="n">
+        <v>20</v>
+      </c>
+      <c r="H118" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>gap, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>SKYQ</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>04/08/26</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>03/02/26</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>5</v>
+      </c>
+      <c r="E119" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F119" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="G119" t="n">
+        <v>44</v>
+      </c>
+      <c r="H119" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>abnormal_candle</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>abnormal_candle, consolidation, gap, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>SKYQ</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>03/26/26</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>03/26/26</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2</v>
+      </c>
+      <c r="H120" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>02/11/26</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>02/11/26</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>436.35</v>
+      </c>
+      <c r="E121" t="n">
+        <v>434.87</v>
+      </c>
+      <c r="F121" t="n">
+        <v>437.83</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2</v>
+      </c>
+      <c r="H121" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>03/11/26</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>02/09/26</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>416.38</v>
+      </c>
+      <c r="E122" t="n">
+        <v>414.9</v>
+      </c>
+      <c r="F122" t="n">
+        <v>418.92</v>
+      </c>
+      <c r="G122" t="n">
+        <v>25</v>
+      </c>
+      <c r="H122" t="n">
+        <v>51.75</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>gap, historical, structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>02/23/26</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>02/06/26</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>411.82</v>
+      </c>
+      <c r="E123" t="n">
+        <v>410.34</v>
+      </c>
+      <c r="F123" t="n">
+        <v>413.84</v>
+      </c>
+      <c r="G123" t="n">
+        <v>21</v>
+      </c>
+      <c r="H123" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>04/08/26</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>04/06/26</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>346.65</v>
+      </c>
+      <c r="E124" t="n">
+        <v>344.79</v>
+      </c>
+      <c r="F124" t="n">
+        <v>348.13</v>
+      </c>
+      <c r="G124" t="n">
+        <v>10</v>
+      </c>
+      <c r="H124" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>04/09/26</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>04/07/26</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>337.25</v>
+      </c>
+      <c r="E125" t="n">
+        <v>335.76</v>
+      </c>
+      <c r="F125" t="n">
+        <v>338.73</v>
+      </c>
+      <c r="G125" t="n">
+        <v>6</v>
+      </c>
+      <c r="H125" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>consolidation, historical, structural</t>
         </is>
       </c>
     </row>
